--- a/Assets/RefData_Excel/Guide.xlsx
+++ b/Assets/RefData_Excel/Guide.xlsx
@@ -1756,7 +1756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1798,6 +1798,11 @@
           <t>策划说明</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>本步超时毫秒；&lt;=0 继承运行器级</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="10" t="inlineStr">
@@ -1830,6 +1835,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>TimeoutMs</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="15" t="inlineStr">
@@ -1860,6 +1870,11 @@
       <c r="F3" s="15" t="inlineStr">
         <is>
           <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>int</t>
         </is>
       </c>
     </row>
@@ -1885,6 +1900,9 @@
         <is>
           <t>高亮领取按钮并等待真实点击</t>
         </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/RefData_Excel/Guide.xlsx
+++ b/Assets/RefData_Excel/Guide.xlsx
@@ -2706,7 +2706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2836,6 +2836,27 @@
       <c r="E5" s="41" t="inlineStr">
         <is>
           <t>点击领取金币按钮完成步骤</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="71" t="n">
+        <v>420003</v>
+      </c>
+      <c r="B6" s="40" t="inlineStr">
+        <is>
+          <t>GuideOverlayClicked</t>
+        </is>
+      </c>
+      <c r="C6" s="72" t="n">
+        <v>2100</v>
+      </c>
+      <c r="D6" s="72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="41" t="inlineStr">
+        <is>
+          <t>孔外压暗区被点击/点任意处继续：对话步骤把 CompleteTriggerId 指向此行（无参，PayloadId 忽略）</t>
         </is>
       </c>
     </row>
